--- a/figures/lecture5/6345.0/634504a.xlsx
+++ b/figures/lecture5/6345.0/634504a.xlsx
@@ -17,62 +17,62 @@
     <sheet name="Enquiries" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="A2704472W">Data1!$B$1:$B$10,Data1!$B$11:$B$36</definedName>
-    <definedName name="A2704472W_Data">Data1!$B$11:$B$36</definedName>
-    <definedName name="A2704472W_Latest">Data1!$B$36</definedName>
-    <definedName name="A2704738V">Data1!$D$1:$D$10,Data1!$D$11:$D$36</definedName>
-    <definedName name="A2704738V_Data">Data1!$D$11:$D$36</definedName>
-    <definedName name="A2704738V_Latest">Data1!$D$36</definedName>
-    <definedName name="A2705004A">Data1!$G$1:$G$10,Data1!$G$11:$G$36</definedName>
-    <definedName name="A2705004A_Data">Data1!$G$11:$G$36</definedName>
-    <definedName name="A2705004A_Latest">Data1!$G$36</definedName>
-    <definedName name="A2705270T">Data1!$J$1:$J$10,Data1!$J$11:$J$36</definedName>
-    <definedName name="A2705270T_Data">Data1!$J$11:$J$36</definedName>
-    <definedName name="A2705270T_Latest">Data1!$J$36</definedName>
-    <definedName name="A2705536R">Data1!$I$1:$I$10,Data1!$I$11:$I$36</definedName>
-    <definedName name="A2705536R_Data">Data1!$I$11:$I$36</definedName>
-    <definedName name="A2705536R_Latest">Data1!$I$36</definedName>
-    <definedName name="A2705802V">Data1!$H$1:$H$10,Data1!$H$11:$H$36</definedName>
-    <definedName name="A2705802V_Data">Data1!$H$11:$H$36</definedName>
-    <definedName name="A2705802V_Latest">Data1!$H$36</definedName>
-    <definedName name="A2706068F">Data1!$F$1:$F$10,Data1!$F$11:$F$36</definedName>
-    <definedName name="A2706068F_Data">Data1!$F$11:$F$36</definedName>
-    <definedName name="A2706068F_Latest">Data1!$F$36</definedName>
-    <definedName name="A2706334K">Data1!$C$1:$C$10,Data1!$C$11:$C$36</definedName>
-    <definedName name="A2706334K_Data">Data1!$C$11:$C$36</definedName>
-    <definedName name="A2706334K_Latest">Data1!$C$36</definedName>
-    <definedName name="A2706600R">Data1!$E$1:$E$10,Data1!$E$11:$E$36</definedName>
-    <definedName name="A2706600R_Data">Data1!$E$11:$E$36</definedName>
-    <definedName name="A2706600R_Latest">Data1!$E$36</definedName>
-    <definedName name="A85020269V">Data1!$K$1:$K$10,Data1!$K$11:$K$36</definedName>
-    <definedName name="A85020269V_Data">Data1!$K$11:$K$36</definedName>
-    <definedName name="A85020269V_Latest">Data1!$K$36</definedName>
-    <definedName name="A85020589F">Data1!$S$1:$S$10,Data1!$S$11:$S$36</definedName>
-    <definedName name="A85020589F_Data">Data1!$S$11:$S$36</definedName>
-    <definedName name="A85020589F_Latest">Data1!$S$36</definedName>
-    <definedName name="A85020853F">Data1!$N$1:$N$10,Data1!$N$11:$N$36</definedName>
-    <definedName name="A85020853F_Data">Data1!$N$11:$N$36</definedName>
-    <definedName name="A85020853F_Latest">Data1!$N$36</definedName>
-    <definedName name="A85021381L">Data1!$L$1:$L$10,Data1!$L$11:$L$36</definedName>
-    <definedName name="A85021381L_Data">Data1!$L$11:$L$36</definedName>
-    <definedName name="A85021381L_Latest">Data1!$L$36</definedName>
-    <definedName name="A85021805F">Data1!$M$1:$M$10,Data1!$M$11:$M$36</definedName>
-    <definedName name="A85021805F_Data">Data1!$M$11:$M$36</definedName>
-    <definedName name="A85021805F_Latest">Data1!$M$36</definedName>
-    <definedName name="A85022137C">Data1!$O$1:$O$10,Data1!$O$11:$O$36</definedName>
-    <definedName name="A85022137C_Data">Data1!$O$11:$O$36</definedName>
-    <definedName name="A85022137C_Latest">Data1!$O$36</definedName>
-    <definedName name="A85022389X">Data1!$P$1:$P$10,Data1!$P$11:$P$36</definedName>
-    <definedName name="A85022389X_Data">Data1!$P$11:$P$36</definedName>
-    <definedName name="A85022389X_Latest">Data1!$P$36</definedName>
-    <definedName name="A85022813X">Data1!$Q$1:$Q$10,Data1!$Q$11:$Q$36</definedName>
-    <definedName name="A85022813X_Data">Data1!$Q$11:$Q$36</definedName>
-    <definedName name="A85022813X_Latest">Data1!$Q$36</definedName>
-    <definedName name="A85023409R">Data1!$R$1:$R$10,Data1!$R$11:$R$36</definedName>
-    <definedName name="A85023409R_Data">Data1!$R$11:$R$36</definedName>
-    <definedName name="A85023409R_Latest">Data1!$R$36</definedName>
-    <definedName name="Date_Range">Data1!$A$2:$A$10,Data1!$A$11:$A$36</definedName>
-    <definedName name="Date_Range_Data">Data1!$A$11:$A$36</definedName>
+    <definedName name="A2704472W">Data1!$B$1:$B$10,Data1!$B$11:$B$38</definedName>
+    <definedName name="A2704472W_Data">Data1!$B$11:$B$38</definedName>
+    <definedName name="A2704472W_Latest">Data1!$B$38</definedName>
+    <definedName name="A2704738V">Data1!$D$1:$D$10,Data1!$D$11:$D$38</definedName>
+    <definedName name="A2704738V_Data">Data1!$D$11:$D$38</definedName>
+    <definedName name="A2704738V_Latest">Data1!$D$38</definedName>
+    <definedName name="A2705004A">Data1!$G$1:$G$10,Data1!$G$11:$G$38</definedName>
+    <definedName name="A2705004A_Data">Data1!$G$11:$G$38</definedName>
+    <definedName name="A2705004A_Latest">Data1!$G$38</definedName>
+    <definedName name="A2705270T">Data1!$J$1:$J$10,Data1!$J$11:$J$38</definedName>
+    <definedName name="A2705270T_Data">Data1!$J$11:$J$38</definedName>
+    <definedName name="A2705270T_Latest">Data1!$J$38</definedName>
+    <definedName name="A2705536R">Data1!$I$1:$I$10,Data1!$I$11:$I$38</definedName>
+    <definedName name="A2705536R_Data">Data1!$I$11:$I$38</definedName>
+    <definedName name="A2705536R_Latest">Data1!$I$38</definedName>
+    <definedName name="A2705802V">Data1!$H$1:$H$10,Data1!$H$11:$H$38</definedName>
+    <definedName name="A2705802V_Data">Data1!$H$11:$H$38</definedName>
+    <definedName name="A2705802V_Latest">Data1!$H$38</definedName>
+    <definedName name="A2706068F">Data1!$F$1:$F$10,Data1!$F$11:$F$38</definedName>
+    <definedName name="A2706068F_Data">Data1!$F$11:$F$38</definedName>
+    <definedName name="A2706068F_Latest">Data1!$F$38</definedName>
+    <definedName name="A2706334K">Data1!$C$1:$C$10,Data1!$C$11:$C$38</definedName>
+    <definedName name="A2706334K_Data">Data1!$C$11:$C$38</definedName>
+    <definedName name="A2706334K_Latest">Data1!$C$38</definedName>
+    <definedName name="A2706600R">Data1!$E$1:$E$10,Data1!$E$11:$E$38</definedName>
+    <definedName name="A2706600R_Data">Data1!$E$11:$E$38</definedName>
+    <definedName name="A2706600R_Latest">Data1!$E$38</definedName>
+    <definedName name="A85020269V">Data1!$K$1:$K$10,Data1!$K$11:$K$38</definedName>
+    <definedName name="A85020269V_Data">Data1!$K$11:$K$38</definedName>
+    <definedName name="A85020269V_Latest">Data1!$K$38</definedName>
+    <definedName name="A85020589F">Data1!$S$1:$S$10,Data1!$S$11:$S$38</definedName>
+    <definedName name="A85020589F_Data">Data1!$S$11:$S$38</definedName>
+    <definedName name="A85020589F_Latest">Data1!$S$38</definedName>
+    <definedName name="A85020853F">Data1!$N$1:$N$10,Data1!$N$11:$N$38</definedName>
+    <definedName name="A85020853F_Data">Data1!$N$11:$N$38</definedName>
+    <definedName name="A85020853F_Latest">Data1!$N$38</definedName>
+    <definedName name="A85021381L">Data1!$L$1:$L$10,Data1!$L$11:$L$38</definedName>
+    <definedName name="A85021381L_Data">Data1!$L$11:$L$38</definedName>
+    <definedName name="A85021381L_Latest">Data1!$L$38</definedName>
+    <definedName name="A85021805F">Data1!$M$1:$M$10,Data1!$M$11:$M$38</definedName>
+    <definedName name="A85021805F_Data">Data1!$M$11:$M$38</definedName>
+    <definedName name="A85021805F_Latest">Data1!$M$38</definedName>
+    <definedName name="A85022137C">Data1!$O$1:$O$10,Data1!$O$11:$O$38</definedName>
+    <definedName name="A85022137C_Data">Data1!$O$11:$O$38</definedName>
+    <definedName name="A85022137C_Latest">Data1!$O$38</definedName>
+    <definedName name="A85022389X">Data1!$P$1:$P$10,Data1!$P$11:$P$38</definedName>
+    <definedName name="A85022389X_Data">Data1!$P$11:$P$38</definedName>
+    <definedName name="A85022389X_Latest">Data1!$P$38</definedName>
+    <definedName name="A85022813X">Data1!$Q$1:$Q$10,Data1!$Q$11:$Q$38</definedName>
+    <definedName name="A85022813X_Data">Data1!$Q$11:$Q$38</definedName>
+    <definedName name="A85022813X_Latest">Data1!$Q$38</definedName>
+    <definedName name="A85023409R">Data1!$R$1:$R$10,Data1!$R$11:$R$38</definedName>
+    <definedName name="A85023409R_Data">Data1!$R$11:$R$38</definedName>
+    <definedName name="A85023409R_Latest">Data1!$R$38</definedName>
+    <definedName name="Date_Range">Data1!$A$2:$A$10,Data1!$A$11:$A$38</definedName>
+    <definedName name="Date_Range_Data">Data1!$A$11:$A$38</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -917,7 +917,7 @@
     <t>Freq.</t>
   </si>
   <si>
-    <t>© Commonwealth of Australia  2023</t>
+    <t>© Commonwealth of Australia  2026</t>
   </si>
 </sst>
 </file>
@@ -1598,10 +1598,10 @@
         <v>35947</v>
       </c>
       <c r="G12" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H12" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I12" s="10" t="s">
         <v>27</v>
@@ -1630,10 +1630,10 @@
         <v>35947</v>
       </c>
       <c r="G13" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H13" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I13" s="10" t="s">
         <v>27</v>
@@ -1662,10 +1662,10 @@
         <v>35947</v>
       </c>
       <c r="G14" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H14" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I14" s="10" t="s">
         <v>27</v>
@@ -1694,10 +1694,10 @@
         <v>35947</v>
       </c>
       <c r="G15" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H15" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I15" s="10" t="s">
         <v>27</v>
@@ -1726,10 +1726,10 @@
         <v>35947</v>
       </c>
       <c r="G16" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H16" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I16" s="10" t="s">
         <v>27</v>
@@ -1758,10 +1758,10 @@
         <v>35947</v>
       </c>
       <c r="G17" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H17" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I17" s="10" t="s">
         <v>27</v>
@@ -1790,10 +1790,10 @@
         <v>35947</v>
       </c>
       <c r="G18" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H18" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I18" s="10" t="s">
         <v>27</v>
@@ -1822,10 +1822,10 @@
         <v>35947</v>
       </c>
       <c r="G19" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H19" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I19" s="10" t="s">
         <v>27</v>
@@ -1854,10 +1854,10 @@
         <v>35947</v>
       </c>
       <c r="G20" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H20" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I20" s="10" t="s">
         <v>27</v>
@@ -1886,10 +1886,10 @@
         <v>35947</v>
       </c>
       <c r="G21" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H21" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I21" s="10" t="s">
         <v>40</v>
@@ -1918,10 +1918,10 @@
         <v>35947</v>
       </c>
       <c r="G22" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H22" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I22" s="10" t="s">
         <v>40</v>
@@ -1950,10 +1950,10 @@
         <v>35947</v>
       </c>
       <c r="G23" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H23" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I23" s="10" t="s">
         <v>40</v>
@@ -1982,10 +1982,10 @@
         <v>35947</v>
       </c>
       <c r="G24" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H24" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I24" s="10" t="s">
         <v>40</v>
@@ -2014,10 +2014,10 @@
         <v>35947</v>
       </c>
       <c r="G25" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H25" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I25" s="10" t="s">
         <v>40</v>
@@ -2046,10 +2046,10 @@
         <v>35947</v>
       </c>
       <c r="G26" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H26" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I26" s="10" t="s">
         <v>40</v>
@@ -2078,10 +2078,10 @@
         <v>35947</v>
       </c>
       <c r="G27" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H27" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I27" s="10" t="s">
         <v>40</v>
@@ -2110,10 +2110,10 @@
         <v>35947</v>
       </c>
       <c r="G28" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H28" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I28" s="10" t="s">
         <v>40</v>
@@ -2142,10 +2142,10 @@
         <v>35947</v>
       </c>
       <c r="G29" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H29" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I29" s="10" t="s">
         <v>40</v>
@@ -2198,7 +2198,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S36"/>
+  <dimension ref="A1:S38"/>
   <sheetFormatPr defaultColWidth="14.7109375" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="16384" width="14.7109375" style="1"/>
@@ -2619,58 +2619,58 @@
         <v>24</v>
       </c>
       <c r="B8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="C8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="D8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="E8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="F8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="G8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="I8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="J8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="K8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="L8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="M8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="N8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="O8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="P8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="Q8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="R8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="S8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.2">
@@ -2678,58 +2678,58 @@
         <v>25</v>
       </c>
       <c r="B9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="N9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="O9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="P9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="Q9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="R9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="S9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.2">
@@ -4305,6 +4305,124 @@
       </c>
       <c r="S36" s="8">
         <v>2.7</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A37" s="9">
+        <v>45444</v>
+      </c>
+      <c r="B37" s="8">
+        <v>150.6</v>
+      </c>
+      <c r="C37" s="8">
+        <v>153</v>
+      </c>
+      <c r="D37" s="8">
+        <v>155.4</v>
+      </c>
+      <c r="E37" s="8">
+        <v>146.30000000000001</v>
+      </c>
+      <c r="F37" s="8">
+        <v>150</v>
+      </c>
+      <c r="G37" s="8">
+        <v>150.4</v>
+      </c>
+      <c r="H37" s="8">
+        <v>149.9</v>
+      </c>
+      <c r="I37" s="8">
+        <v>143.80000000000001</v>
+      </c>
+      <c r="J37" s="8">
+        <v>151.5</v>
+      </c>
+      <c r="K37" s="8">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="L37" s="8">
+        <v>2.7</v>
+      </c>
+      <c r="M37" s="8">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="N37" s="8">
+        <v>2.5</v>
+      </c>
+      <c r="O37" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="P37" s="8">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="Q37" s="8">
+        <v>3.4</v>
+      </c>
+      <c r="R37" s="8">
+        <v>2.8</v>
+      </c>
+      <c r="S37" s="8">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A38" s="9">
+        <v>45809</v>
+      </c>
+      <c r="B38" s="8">
+        <v>155.5</v>
+      </c>
+      <c r="C38" s="8">
+        <v>157.4</v>
+      </c>
+      <c r="D38" s="8">
+        <v>161.69999999999999</v>
+      </c>
+      <c r="E38" s="8">
+        <v>150.9</v>
+      </c>
+      <c r="F38" s="8">
+        <v>155.30000000000001</v>
+      </c>
+      <c r="G38" s="8">
+        <v>156.4</v>
+      </c>
+      <c r="H38" s="8">
+        <v>154.69999999999999</v>
+      </c>
+      <c r="I38" s="8">
+        <v>150.1</v>
+      </c>
+      <c r="J38" s="8">
+        <v>156.80000000000001</v>
+      </c>
+      <c r="K38" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="L38" s="8">
+        <v>2.9</v>
+      </c>
+      <c r="M38" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="N38" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="O38" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="P38" s="8">
+        <v>4</v>
+      </c>
+      <c r="Q38" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="R38" s="8">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="S38" s="8">
+        <v>3.5</v>
       </c>
     </row>
   </sheetData>
